--- a/artfynd/A 36129-2024 artfynd.xlsx
+++ b/artfynd/A 36129-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>114707674</v>
       </c>
       <c r="B2" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -712,7 +707,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Finsjölund (Finsjölund), Sm</t>
+          <t>Finsjölund, Finsjölund, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -778,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114702402</v>
+        <v>114714787</v>
       </c>
       <c r="B3" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -794,16 +784,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -813,21 +803,23 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Finsjölund, Sm</t>
+          <t>Läggevi 8:54, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573360</v>
+        <v>572917</v>
       </c>
       <c r="R3" t="n">
-        <v>6334360</v>
+        <v>6334006</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,12 +866,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -889,16 +881,11 @@
         <v>114714847</v>
       </c>
       <c r="B4" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1003,16 +990,11 @@
         <v>114718786</v>
       </c>
       <c r="B5" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1121,6 +1103,109 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114702402</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Finsjölund, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>573360</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6334360</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36129-2024 artfynd.xlsx
+++ b/artfynd/A 36129-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114707674</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114714787</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114714847</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114718786</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1206,8 +1231,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114702402</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>